--- a/test_data/fixtures/gb/gb_fip_ZQ9_VALFLDGR.xlsx
+++ b/test_data/fixtures/gb/gb_fip_ZQ9_VALFLDGR.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,45 +487,79 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GB_IGNORE_FIELD</t>
+          <t>GB_DIFF_YELLOW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ignore field test</t>
+          <t>Diff yellow match</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GB_IGNORE_FIELD_FIP</t>
+          <t>GB_FIP_FIELD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>GB_DIFF_GREEN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Diff green match</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GB_FIP_FIELD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GB_IGNORE_FIELD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ignore field test</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>GB_IGNORE_FIELD_FIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>GB_UNMAPPED</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Unmapped field test</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>UNMAPPED_FIELD</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Blank ValidRule test</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>GB_FIP_FIELD</t>
         </is>
